--- a/out/Attention-S4_repeat_2_000001.xlsx
+++ b/out/Attention-S4_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>3.996122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>3.996122136721797</v>
+        <v>4.726153625547767</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.0899601950856026</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.0899601950856026</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.0899601950856026</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.0899601950856026</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC43" t="n">
-        <v>-3.823488901765086e-05</v>
+        <v>-4.36472085271962e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.0164628331025979</v>
+        <v>0.01879322074256499</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.0329696011541154</v>
+        <v>0.03763659562252637</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.06360380332099881</v>
+        <v>0.07260732320729468</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1437581307437981</v>
+        <v>0.1641077367426678</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.01956539545792371</v>
+        <v>0.02233441963428837</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1192029444414931</v>
+        <v>0.1360767003722312</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.003967386336588986</v>
+        <v>0.004530027381869203</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1075444986531238</v>
+        <v>0.1227683748818019</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.003435095476695675</v>
+        <v>0.003921935211170817</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1104433786054307</v>
+        <v>0.1260782097493152</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001676442581929727</v>
+        <v>0.001914448609346924</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.11035832090681</v>
+        <v>0.1259818222433729</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0007974741049397474</v>
+        <v>0.0009110632788279714</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1102750209581912</v>
+        <v>0.1258874435512728</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.000329582832027443</v>
+        <v>0.0003769031992858999</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.110135122268657</v>
+        <v>0.1257284660121372</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002265014470078366</v>
+        <v>0.0002596833210789598</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1102590118166688</v>
+        <v>0.1258705836610114</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>9.16430535496559e-05</v>
+        <v>0.0001051730810466077</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1102154172815937</v>
+        <v>0.1258216037462773</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>4.511287083304001e-05</v>
+        <v>5.246275855521921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1102139231631134</v>
+        <v>0.1258205964031885</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.494483528510883e-05</v>
+        <v>1.756915571736e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1101979720362679</v>
+        <v>0.1258032043385999</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.880031965381889e-06</v>
+        <v>7.025298488053667e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1101947650205477</v>
+        <v>0.1258002338846342</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>8.204558969451803e-08</v>
+        <v>1.211389054071076e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.110189602085982</v>
+        <v>0.1257950444848361</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1101842770536372</v>
+        <v>0.1257896875681134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.077656293461284e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1101789160511354</v>
+        <v>0.125784253674136</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1101737714772017</v>
+        <v>0.1257791091002023</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.110168443682879</v>
+        <v>0.1257737813058796</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.1257738211613519</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1101685233938235</v>
+        <v>0.1257738610168241</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1101685154227291</v>
+        <v>0.1257738530457297</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1101686748446182</v>
+        <v>0.1257740124676188</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.110168929919641</v>
+        <v>0.1257742675426416</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1101686828157126</v>
+        <v>0.1257740204387132</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7562253596518723</v>
+        <v>5.326153625547767</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1101686429602404</v>
+        <v>0.125773980583241</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.0899601950856026</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.1257739885543354</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1101686828157126</v>
+        <v>0.1257740204387132</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1101687784688463</v>
+        <v>0.125774116091847</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1101687147000905</v>
+        <v>0.1257740523230911</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1101686748446182</v>
+        <v>0.1257740124676188</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.1257739885543354</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1101684038274067</v>
+        <v>0.1257737414504073</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1101683241164619</v>
+        <v>0.1257736617394625</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1101683719430286</v>
+        <v>0.1257737095660293</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1101684915094457</v>
+        <v>0.1257738291324463</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1101684755672568</v>
+        <v>0.1257738131902574</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1101684915094457</v>
+        <v>0.1257738291324463</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1101684755672568</v>
+        <v>0.1257738131902574</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.110168531364918</v>
+        <v>0.1257738689879186</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.110168531364918</v>
+        <v>0.1257738689879186</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.110168531364918</v>
+        <v>0.1257738689879186</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1101686828157126</v>
+        <v>0.1257740204387132</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1101688980352632</v>
+        <v>0.1257742356582638</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1101688103532242</v>
+        <v>0.1257741479762248</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1101687625266574</v>
+        <v>0.125774100149658</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1101688103532242</v>
+        <v>0.1257741479762248</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1101686270180515</v>
+        <v>0.1257739646410521</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1101686349891459</v>
+        <v>0.1257739726121465</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1101686429602404</v>
+        <v>0.125773980583241</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.1257739885543354</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.1257739885543354</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1101686907868071</v>
+        <v>0.1257740284098077</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.110168754555563</v>
+        <v>0.1257740921785636</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1101688661508854</v>
+        <v>0.125774203773886</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1101689139774521</v>
+        <v>0.1257742516004527</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1101688741219798</v>
+        <v>0.1257742117449804</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1101688023821297</v>
+        <v>0.1257741400051303</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1101689219485465</v>
+        <v>0.1257742595715471</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1101687625266574</v>
+        <v>0.125774100149658</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.110168531364918</v>
+        <v>0.1257738689879186</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.1257738211613519</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1101685154227291</v>
+        <v>0.1257738530457297</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1101684994805402</v>
+        <v>0.1257738371035408</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1101683799141231</v>
+        <v>0.1257737175371237</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1101683400586508</v>
+        <v>0.1257736776816514</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.1257738211613519</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.110168619046957</v>
+        <v>0.1257739566699576</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1101686031047681</v>
+        <v>0.1257739407277687</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1101685393360124</v>
+        <v>0.125773876959013</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1101684357117845</v>
+        <v>0.1257737733347851</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1101683161453675</v>
+        <v>0.1257736537683681</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1101684357117845</v>
+        <v>0.1257737733347851</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.1257738211613519</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.1257739168144853</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1101684596250679</v>
+        <v>0.1257737972480685</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>4.596122136721797</v>
+        <v>-0.6899601950856026</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1101684675961623</v>
+        <v>0.125773805219163</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000001.xlsx
+++ b/out/Attention-S4_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>3.996122136721797</v>
+        <v>2.84</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>3.996122136721797</v>
+        <v>1.775719917793858</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877156</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>4.596122136721797</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.7114398355877154</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1562253596518723</v>
+        <v>-0.1528402466184268</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC43" t="n">
-        <v>-3.823488901765086e-05</v>
+        <v>-7.118155094620306e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.0164628331025979</v>
+        <v>0.03064860208318053</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.0329696011541154</v>
+        <v>0.06137921215296304</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.06360380332099881</v>
+        <v>0.1184125858377957</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1437581307437981</v>
+        <v>0.2676339444646891</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.01956539545792371</v>
+        <v>0.03642386617873211</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1192029444414931</v>
+        <v>0.2219202098048567</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.003967386336588986</v>
+        <v>0.007390773916284417</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1075444986531238</v>
+        <v>0.2002199962201908</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.003435095476695675</v>
+        <v>0.0063990903307061</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1104433786054307</v>
+        <v>0.2056208663915505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001676442581929727</v>
+        <v>0.003125479278263839</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>4.596122136721797</v>
+        <v>3.04</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.11035832090681</v>
+        <v>0.2054668301601184</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0007974741049397474</v>
+        <v>0.0014890317224357</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>4.596122136721797</v>
+        <v>1.975719917793858</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1102750209581912</v>
+        <v>0.2053160802144229</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.000329582832027443</v>
+        <v>0.0006174020069994697</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.110135122268657</v>
+        <v>0.2050600256325789</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002265014470078366</v>
+        <v>0.0004263643629246022</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1102590118166688</v>
+        <v>0.205295004017496</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>9.16430535496559e-05</v>
+        <v>0.0001754003666260243</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1102154172815937</v>
+        <v>0.2052181989553771</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>4.511287083304001e-05</v>
+        <v>8.854402555500802e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1102139231631134</v>
+        <v>0.2052196986294184</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.494483528510883e-05</v>
+        <v>3.174048605151627e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1101979720362679</v>
+        <v>0.2051945255010186</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.880031965381889e-06</v>
+        <v>1.504216414675611e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1101947650205477</v>
+        <v>0.2051928283667972</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>8.204558969451803e-08</v>
+        <v>4.599419447200756e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.110189602085982</v>
+        <v>0.205187527686924</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.335871922010791e-06</v>
+        <v>-2.045694596194254e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1101842770536372</v>
+        <v>0.2051819426287033</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.077656293461284e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1101789160511354</v>
+        <v>0.2051762923635501</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.586597321616299e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1101737714772017</v>
+        <v>0.2051710510422492</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051657631033987</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.110168443682879</v>
+        <v>0.2051604912693477</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.20516053112482</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1101685233938235</v>
+        <v>0.2051605709802923</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1101685154227291</v>
+        <v>0.2051605630091978</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1101686748446182</v>
+        <v>0.2051607224310869</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.110168929919641</v>
+        <v>0.2051609775061098</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1101686828157126</v>
+        <v>0.2051607304021814</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1101686429602404</v>
+        <v>0.2051606905467091</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.2051606985178036</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1101686828157126</v>
+        <v>0.2051607304021814</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1101687784688463</v>
+        <v>0.2051608260553151</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1101687147000905</v>
+        <v>0.2051607622865592</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1101686748446182</v>
+        <v>0.2051607224310869</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.2051606985178036</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1101684038274067</v>
+        <v>0.2051604514138755</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1101683241164619</v>
+        <v>0.2051603717029307</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1101683719430286</v>
+        <v>0.2051604195294974</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1101684915094457</v>
+        <v>0.2051605390959144</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1101684755672568</v>
+        <v>0.2051605231537255</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1101684915094457</v>
+        <v>0.2051605390959144</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1101684755672568</v>
+        <v>0.2051605231537255</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.110168531364918</v>
+        <v>0.2051605789513867</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.110168531364918</v>
+        <v>0.2051605789513867</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.110168531364918</v>
+        <v>0.2051605789513867</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1101686828157126</v>
+        <v>0.2051607304021814</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1101688980352632</v>
+        <v>0.2051609456217319</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1101688103532242</v>
+        <v>0.2051608579396929</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1101687625266574</v>
+        <v>0.2051608101131262</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1101688103532242</v>
+        <v>0.2051608579396929</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1101686270180515</v>
+        <v>0.2051606746045202</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1101686349891459</v>
+        <v>0.2051606825756147</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1101686429602404</v>
+        <v>0.2051606905467091</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.2051606985178036</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1101686509313348</v>
+        <v>0.2051606985178036</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1101686907868071</v>
+        <v>0.2051607383732758</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.110168754555563</v>
+        <v>0.2051608021420317</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1101688661508854</v>
+        <v>0.2051609137373541</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1101689139774521</v>
+        <v>0.2051609615639208</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1101688741219798</v>
+        <v>0.2051609217084485</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1101688023821297</v>
+        <v>0.2051608499685985</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1101689219485465</v>
+        <v>0.2051609695350153</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1101687625266574</v>
+        <v>0.2051608101131262</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.110168531364918</v>
+        <v>0.2051605789513867</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.20516053112482</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1101685154227291</v>
+        <v>0.2051605630091978</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1101684994805402</v>
+        <v>0.2051605470670089</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1101683799141231</v>
+        <v>0.2051604275005919</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1101683400586508</v>
+        <v>0.2051603876451196</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.20516053112482</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.110168619046957</v>
+        <v>0.2051606666334257</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1101686031047681</v>
+        <v>0.2051606506912368</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1101685393360124</v>
+        <v>0.2051605869224812</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1101684357117845</v>
+        <v>0.2051604832982533</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1101683161453675</v>
+        <v>0.2051603637318362</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1101684357117845</v>
+        <v>0.2051604832982533</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1101684835383513</v>
+        <v>0.20516053112482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7562253596518723</v>
+        <v>-0.3528402466184268</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1101685791914847</v>
+        <v>0.2051606267779535</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7562253596518723</v>
+        <v>0.9114398355877155</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1101684596250679</v>
+        <v>0.2051605072115366</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>4.596122136721797</v>
+        <v>1.443579876690787</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1101684675961623</v>
+        <v>0.2051605151826311</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000001.xlsx
+++ b/out/Attention-S4_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.001144766807556152</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.84</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.001145780086517334</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.775719917793858</v>
+        <v>-0.09000000000000005</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001160714775323868</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9114398355877156</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002719927579164505</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.00274958461523056</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0001985840499401093</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004103008657693863</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9114398355877155</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.004166468977928162</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.003167640417814255</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.006372906267642975</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.00495508685708046</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.006003614515066147</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.00349956750869751</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001534655690193176</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.7114398355877154</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0003593489527702332</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.975719917793858</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0002151206135749817</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.975719917793858</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001193072646856308</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001674607396125793</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001908078789710999</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.004139397293329239</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.004053205251693726</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.002501934766769409</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001188471913337708</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.000986490398645401</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.002005692571401596</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002229224890470505</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.003218885511159897</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.004648797214031219</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.004407219588756561</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.00018325075507164</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002596020698547363</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001036319881677628</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.003587827086448669</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.004297740757465363</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.004952728748321533</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.003897033631801605</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.004119832068681717</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.00493280217051506</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.001679897308349609</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0002382770180702209</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.000941932201385498</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.002386000007390976</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.118155094620306e-05</v>
+        <v>-0.0001473718101831619</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03064860208318053</v>
+        <v>0.06345391560930431</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.003136627376079559</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.9114398355877155</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06137921215296304</v>
+        <v>0.1270773879135698</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1184125858377957</v>
+        <v>0.2451568611862512</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001960478723049164</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.975719917793858</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2676339444646891</v>
+        <v>0.5540992489817671</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03642386617873211</v>
+        <v>0.07541111576779003</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.004540160298347473</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.04</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2219202098048567</v>
+        <v>0.4594552905944062</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.007390773916284417</v>
+        <v>0.01530147634608275</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01349698379635811</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2002199962201908</v>
+        <v>0.4145285482217036</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0063990903307061</v>
+        <v>0.01325175855749444</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01970457658171654</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2056208663915505</v>
+        <v>0.4257139759042717</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003125479278263839</v>
+        <v>0.006477164158480131</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01919064298272133</v>
       </c>
       <c r="JB49" t="n">
-        <v>3.04</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2054668301601184</v>
+        <v>0.4254004052695686</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0014890317224357</v>
+        <v>0.003088634559426337</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.006563927978277206</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.975719917793858</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2053160802144229</v>
+        <v>0.4250936724324035</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006174020069994697</v>
+        <v>0.001283784120039152</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.005121476948261261</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9114398355877155</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2050600256325789</v>
+        <v>0.4245690543520839</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004263643629246022</v>
+        <v>0.0008878239139602231</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01246126368641853</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.205295004017496</v>
+        <v>0.4250605235650672</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001754003666260243</v>
+        <v>0.0003680421867016718</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0136171355843544</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2052181989553771</v>
+        <v>0.4249070409544716</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>8.854402555500802e-05</v>
+        <v>0.0001881015956099809</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01658859476447105</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2052196986294184</v>
+        <v>0.4249154820520258</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.174048605151627e-05</v>
+        <v>7.110529253528369e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009768161922693253</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2051945255010186</v>
+        <v>0.4248686948574835</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.504216414675611e-05</v>
+        <v>3.622959481618401e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.008158732205629349</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2051928283667972</v>
+        <v>0.4248705371507951</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.599419447200756e-06</v>
+        <v>1.532818235877807e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.009000729769468307</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.205187527686924</v>
+        <v>0.4248649093258159</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>4.59086108076115e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.00434454157948494</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2051819426287033</v>
+        <v>0.4248587073249966</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.155312586922569e-06</v>
+        <v>-8.494533205757797e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.004032637923955917</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2051762923635501</v>
+        <v>0.4248523339032144</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.005693946033716202</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2051710510422492</v>
+        <v>0.4248468501663788</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>-4.36427134277522e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003434959799051285</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2051657631033987</v>
+        <v>0.4248413699418115</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.007093731313943863</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2051604912693477</v>
+        <v>0.4248359625991546</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01458349451422691</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.20516053112482</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02195776998996735</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2051605709802923</v>
+        <v>0.4248310813009055</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01586310192942619</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2051605630091978</v>
+        <v>0.424831073329811</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01063727587461472</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2051607224310869</v>
+        <v>0.4248312327517001</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.003405418246984482</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.004655245691537857</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2051609775061098</v>
+        <v>0.4248314878267229</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004041794687509537</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2051607304021814</v>
+        <v>0.4248312407227945</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.005502328276634216</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2051606905467091</v>
+        <v>0.4248312008673223</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.009827174246311188</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01139992475509644</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2051606985178036</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.009499341249465942</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0004568547010421753</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2051607304021814</v>
+        <v>0.4248312407227945</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01053695753216743</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2051608260553151</v>
+        <v>0.4248313363759282</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01097138971090317</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2051607622865592</v>
+        <v>0.4248312726071723</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01104151457548141</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2051607224310869</v>
+        <v>0.4248312327517001</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.008525244891643524</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2051606985178036</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004326596856117249</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2051604514138755</v>
+        <v>0.4248309617344886</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003663040697574615</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2051603717029307</v>
+        <v>0.4248308820235438</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002991922199726105</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2051604195294974</v>
+        <v>0.4248309298501106</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004457615315914154</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2051605390959144</v>
+        <v>0.4248310494165276</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.006518092006444931</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2051605231537255</v>
+        <v>0.4248310334743387</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01205209642648697</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2051605390959144</v>
+        <v>0.4248310494165276</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01684268936514854</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2051605231537255</v>
+        <v>0.4248310334743387</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01809443533420563</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2051605789513867</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01695899292826653</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2051605789513867</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01933307200670242</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2051605789513867</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01307849958539009</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2051607304021814</v>
+        <v>0.4248312407227945</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.005051970481872559</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2051609456217319</v>
+        <v>0.4248314559423451</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004464052617549896</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2051608579396929</v>
+        <v>0.4248313682603061</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008427698165178299</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2051608101131262</v>
+        <v>0.4248313204337393</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01184738799929619</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2051608579396929</v>
+        <v>0.4248313682603061</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01458093151450157</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2051606746045202</v>
+        <v>0.4248311849251334</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01280886679887772</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2051606825756147</v>
+        <v>0.4248311928962278</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01120201870799065</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2051606905467091</v>
+        <v>0.4248312008673223</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01002571731805801</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2051606985178036</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.008371632546186447</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2051606985178036</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003658544272184372</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2051607383732758</v>
+        <v>0.424831248693889</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00268838182091713</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2051608021420317</v>
+        <v>0.4248313124626449</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001589972525835037</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2051609137373541</v>
+        <v>0.4248314240579673</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001246824860572815</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2051609615639208</v>
+        <v>0.424831471884534</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.001615051180124283</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2051609217084485</v>
+        <v>0.4248314320290617</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003305733203887939</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2051608499685985</v>
+        <v>0.4248313602892116</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005124356597661972</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2051609695350153</v>
+        <v>0.4248314798556285</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.005428679287433624</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2051608101131262</v>
+        <v>0.4248313204337393</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004289738833904266</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2051605789513867</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.007273439317941666</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.20516053112482</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.008626300841569901</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2051605630091978</v>
+        <v>0.424831073329811</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.007223125547170639</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.006696298718452454</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.006455712020397186</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2051605470670089</v>
+        <v>0.4248310573876221</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.006284676492214203</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2051604275005919</v>
+        <v>0.424830937821205</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002887994050979614</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2051603876451196</v>
+        <v>0.4248308979657328</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.0003359168767929077</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.20516053112482</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003047149628400803</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2051606666334257</v>
+        <v>0.4248311769540389</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003997169435024261</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2051606506912368</v>
+        <v>0.42483116101185</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002303298562765121</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002174977213144302</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2051605869224812</v>
+        <v>0.4248310972430944</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0004153475165367126</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2051604832982533</v>
+        <v>0.4248309936188664</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0004503317177295685</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3528402466184268</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2051603637318362</v>
+        <v>0.4248308740524493</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003259856253862381</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2051604832982533</v>
+        <v>0.4248309936188664</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003357268869876862</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.20516053112482</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.005842834711074829</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3528402466184268</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2051606267779535</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004444368183612823</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9114398355877155</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2051605072115366</v>
+        <v>0.4248310175321498</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0009935945272445679</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.443579876690787</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2051605151826311</v>
+        <v>0.4248310255032443</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000001.xlsx
+++ b/out/Attention-S4_repeat_2_000001.xlsx
@@ -53414,7 +53414,7 @@
         <v>-0.01063727587461472</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.4248312327517001</v>
@@ -54209,7 +54209,7 @@
         <v>-0.003405418246984482</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC67" t="n">
         <v>0.4248311370985666</v>
@@ -55004,7 +55004,7 @@
         <v>-0.004655245691537857</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
         <v>0.4248314878267229</v>
@@ -55799,7 +55799,7 @@
         <v>-0.004041794687509537</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
         <v>0.4248312407227945</v>
@@ -56594,7 +56594,7 @@
         <v>-0.005502328276634216</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0.4248312008673223</v>
@@ -62954,7 +62954,7 @@
         <v>-0.008525244891643524</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
         <v>0.4248312088384167</v>
